--- a/ExcelAnalyticsPlatform/ExcelAnalytics.API/Uploads/TestPMAllocation.xlsx
+++ b/ExcelAnalyticsPlatform/ExcelAnalytics.API/Uploads/TestPMAllocation.xlsx
@@ -3066,7 +3066,7 @@
         <v>60</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>35</v>
@@ -3136,8 +3136,8 @@
       <c r="O16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="3" t="s">
-        <v>48</v>
+      <c r="P16" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>35</v>
@@ -3208,7 +3208,7 @@
         <v>60</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q17" s="7" t="s">
         <v>35</v>
@@ -3278,8 +3278,8 @@
       <c r="O18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>48</v>
+      <c r="P18" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>35</v>
@@ -3348,7 +3348,7 @@
         <v>41</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q19" s="7" t="s">
         <v>42</v>
@@ -3419,7 +3419,7 @@
         <v>60</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>35</v>
@@ -3490,7 +3490,7 @@
         <v>58</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>35</v>
@@ -3561,7 +3561,7 @@
         <v>60</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>35</v>
@@ -3632,7 +3632,7 @@
         <v>60</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q23" s="7" t="s">
         <v>35</v>
@@ -3701,7 +3701,7 @@
         <v>82</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>42</v>
@@ -3772,7 +3772,7 @@
         <v>47</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q25" s="7" t="s">
         <v>35</v>
